--- a/sunrise Due Details soft.xlsx
+++ b/sunrise Due Details soft.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cwc\Desktop\opencode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA4502B-7430-49C2-8633-D91A51EFA21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ED30C1-AB17-49CE-AA7B-406F75852EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="476">
   <si>
     <t>Sunrise Apartment Welfare Society</t>
   </si>
@@ -188,9 +188,6 @@
     <t>Mukul Agrawal</t>
   </si>
   <si>
-    <t>D-5 (Store)</t>
-  </si>
-  <si>
     <t>E-5</t>
   </si>
   <si>
@@ -311,9 +308,6 @@
     <t>Mona Sherpa</t>
   </si>
   <si>
-    <t>E-9</t>
-  </si>
-  <si>
     <t>A-10</t>
   </si>
   <si>
@@ -374,15 +368,9 @@
     <t>Uma Keyal</t>
   </si>
   <si>
-    <t>F-1</t>
-  </si>
-  <si>
     <t>G-1</t>
   </si>
   <si>
-    <t xml:space="preserve"> Deepti Sharma</t>
-  </si>
-  <si>
     <t>H-1</t>
   </si>
   <si>
@@ -494,9 +482,6 @@
     <t>k-4</t>
   </si>
   <si>
-    <t xml:space="preserve">  Pragati Aryal</t>
-  </si>
-  <si>
     <t>L2-4</t>
   </si>
   <si>
@@ -812,9 +797,6 @@
     <t>Sarada Jyoti Shrestha</t>
   </si>
   <si>
-    <t>H-12 (Store)</t>
-  </si>
-  <si>
     <t>I-12</t>
   </si>
   <si>
@@ -845,9 +827,6 @@
     <t>Ayush Kedia</t>
   </si>
   <si>
-    <t>F-13 (Store)</t>
-  </si>
-  <si>
     <t>G-13</t>
   </si>
   <si>
@@ -923,9 +902,6 @@
     <t>Shambhu Shah Teli</t>
   </si>
   <si>
-    <t>k-14 (Store)</t>
-  </si>
-  <si>
     <t>N-1</t>
   </si>
   <si>
@@ -1004,9 +980,6 @@
     <t>Jog Maya Gurung</t>
   </si>
   <si>
-    <t>N-3 (Store)</t>
-  </si>
-  <si>
     <t>O1-3</t>
   </si>
   <si>
@@ -1103,12 +1076,6 @@
     <t>Priti Rajya Laxmi Rana</t>
   </si>
   <si>
-    <t>Q-5 (Store)</t>
-  </si>
-  <si>
-    <t>Q-5 (Store-2)</t>
-  </si>
-  <si>
     <t>M-6</t>
   </si>
   <si>
@@ -1476,6 +1443,12 @@
   </si>
   <si>
     <t>BII</t>
+  </si>
+  <si>
+    <t>Pragati Aryal</t>
+  </si>
+  <si>
+    <t>Deepti Sharma</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1459,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1524,12 +1497,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1624,9 +1591,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="43" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1648,6 +1612,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1964,25 +1931,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E5" s="2"/>
@@ -2371,42 +2338,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G259"/>
+  <dimension ref="A1:G250"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>481</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="A3" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -2422,7 +2389,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -2430,7 +2397,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>5</v>
@@ -2439,7 +2406,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="9">
-        <v>0</v>
+        <v>3914</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -2447,7 +2414,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>7</v>
@@ -2456,7 +2423,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="9">
-        <v>18791</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -2464,7 +2431,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>9</v>
@@ -2473,7 +2440,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="9">
-        <v>5829</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -2481,7 +2448,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>11</v>
@@ -2490,7 +2457,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="9">
-        <v>0</v>
+        <v>5781</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -2498,7 +2465,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>13</v>
@@ -2507,7 +2474,8 @@
         <v>14</v>
       </c>
       <c r="D9" s="9">
-        <v>14444</v>
+        <f>18292-7957-14900</f>
+        <v>-4565</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -2515,7 +2483,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>15</v>
@@ -2524,7 +2492,8 @@
         <v>16</v>
       </c>
       <c r="D10" s="9">
-        <v>64544</v>
+        <f>72410-10000-20000</f>
+        <v>42410</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -2532,7 +2501,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>17</v>
@@ -2541,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="9">
-        <v>738</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -2549,7 +2518,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>19</v>
@@ -2566,7 +2535,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>21</v>
@@ -2583,7 +2552,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>23</v>
@@ -2592,7 +2561,7 @@
         <v>24</v>
       </c>
       <c r="D14" s="9">
-        <v>1001</v>
+        <v>6017</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2600,7 +2569,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>25</v>
@@ -2617,7 +2586,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>27</v>
@@ -2634,7 +2603,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>28</v>
@@ -2651,7 +2620,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>30</v>
@@ -2668,7 +2637,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>32</v>
@@ -2685,7 +2654,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>34</v>
@@ -2702,7 +2671,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>36</v>
@@ -2719,7 +2688,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>38</v>
@@ -2736,7 +2705,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>40</v>
@@ -2745,7 +2714,7 @@
         <v>41</v>
       </c>
       <c r="D23" s="9">
-        <v>5462</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2753,7 +2722,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>42</v>
@@ -2762,7 +2731,7 @@
         <v>43</v>
       </c>
       <c r="D24" s="9">
-        <v>19622</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -2770,7 +2739,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>44</v>
@@ -2779,7 +2748,8 @@
         <v>45</v>
       </c>
       <c r="D25" s="9">
-        <v>7781</v>
+        <f>13055-4495</f>
+        <v>8560</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -2787,7 +2757,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>46</v>
@@ -2804,7 +2774,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>48</v>
@@ -2821,7 +2791,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>50</v>
@@ -2838,7 +2808,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>51</v>
@@ -2855,7 +2825,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>53</v>
@@ -2864,7 +2834,7 @@
         <v>54</v>
       </c>
       <c r="D30" s="9">
-        <v>14510</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2872,16 +2842,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>55</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D31" s="9">
-        <v>544</v>
+        <v>4018</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2889,13 +2859,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D32" s="9">
         <v>0</v>
@@ -2906,13 +2876,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33" s="9">
         <v>0</v>
@@ -2923,16 +2893,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D34" s="9">
-        <v>0</v>
+        <v>9635</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2940,16 +2910,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" s="9">
-        <v>6491</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2957,16 +2927,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D36" s="9">
-        <v>15763</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2974,13 +2944,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D37" s="9">
         <v>0</v>
@@ -2991,16 +2961,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D38" s="9">
-        <v>8458</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -3008,13 +2978,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D39" s="9">
         <v>0</v>
@@ -3025,16 +2995,17 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" s="9">
-        <v>0</v>
+        <f>13424-4865</f>
+        <v>8559</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -3042,16 +3013,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D41" s="9">
-        <v>7781</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -3059,13 +3030,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D42" s="9">
         <v>0</v>
@@ -3076,16 +3047,17 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D43" s="9">
-        <v>0</v>
+        <f>11741-7643</f>
+        <v>4098</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -3093,16 +3065,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D44" s="9">
-        <v>7633</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -3110,13 +3082,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D45" s="9">
         <v>0</v>
@@ -3127,13 +3099,13 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D46" s="9">
         <v>0</v>
@@ -3144,16 +3116,17 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D47" s="9">
-        <v>0</v>
+        <f>24130-17932</f>
+        <v>6198</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -3161,16 +3134,17 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D48" s="9">
-        <v>0</v>
+        <f>6067-4992</f>
+        <v>1075</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -3178,13 +3152,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D49" s="9">
         <v>0</v>
@@ -3195,13 +3169,13 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D50" s="9">
         <v>0</v>
@@ -3212,16 +3186,17 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D51" s="9">
-        <v>4109</v>
+        <f>16398-6000</f>
+        <v>10398</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -3229,16 +3204,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D52" s="9">
-        <v>0</v>
+        <v>11506</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -3246,16 +3221,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D53" s="9">
-        <v>11564</v>
+        <v>0</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3263,16 +3238,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D54" s="9">
-        <v>7633</v>
+        <v>0</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -3280,16 +3255,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D55" s="9">
-        <v>0</v>
+        <v>3866</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -3297,16 +3272,16 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D56" s="9">
-        <v>4529</v>
+        <v>19285</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -3314,13 +3289,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D57" s="9">
         <v>0</v>
@@ -3331,16 +3306,16 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D58" s="9">
-        <v>14627</v>
+        <v>24645</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -3348,16 +3323,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D59" s="9">
-        <v>16588</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3365,16 +3340,16 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D60" s="9">
-        <v>16326</v>
+        <v>0</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3382,33 +3357,31 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D61" s="9">
-        <v>0</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="D61" s="9"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D62" s="9">
-        <v>0</v>
+        <v>57565</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -3416,26 +3389,30 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="9"/>
+        <v>472</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D63" s="9">
+        <v>0</v>
+      </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D64" s="9">
         <v>0</v>
@@ -3446,16 +3423,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D65" s="9">
-        <v>50689</v>
+        <v>15017</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -3463,13 +3440,13 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D66" s="9">
         <v>0</v>
@@ -3480,13 +3457,13 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D67" s="9">
         <v>0</v>
@@ -3497,16 +3474,16 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D68" s="9">
-        <v>8361</v>
+        <v>6072</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -3514,16 +3491,16 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D69" s="9">
-        <v>0</v>
+        <v>6134</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -3531,13 +3508,13 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D70" s="9">
         <v>0</v>
@@ -3548,16 +3525,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D71" s="9">
-        <v>0</v>
+        <v>2144</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -3565,13 +3542,13 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D72" s="9">
         <v>0</v>
@@ -3582,16 +3559,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D73" s="9">
-        <v>0</v>
+        <v>8764</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -3599,13 +3576,13 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D74" s="9">
         <v>0</v>
@@ -3616,16 +3593,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D75" s="9">
-        <v>6967</v>
+        <v>21341</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -3633,13 +3610,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D76" s="9">
         <v>0</v>
@@ -3650,33 +3627,31 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D77" s="9">
-        <v>7631</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D77" s="9"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D78" s="9">
-        <v>15827</v>
+        <v>0</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -3684,16 +3659,17 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D79" s="9">
-        <v>0</v>
+        <f>14948-3950-6564</f>
+        <v>4434</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -3701,13 +3677,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>474</v>
       </c>
       <c r="D80" s="9">
         <v>0</v>
@@ -3718,13 +3694,13 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D81" s="9">
         <v>0</v>
@@ -3735,16 +3711,17 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D82" s="9">
-        <v>10514</v>
+        <f>37579-15000</f>
+        <v>22579</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -3752,13 +3729,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D83" s="9">
         <v>0</v>
@@ -3769,16 +3746,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D84" s="9">
-        <v>11950</v>
+        <v>111911</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -3786,16 +3763,16 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D85" s="9">
-        <v>28718</v>
+        <v>0</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -3803,15 +3780,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D86" s="9">
+        <f>17112-11420-5692</f>
         <v>0</v>
       </c>
       <c r="E86" s="3"/>
@@ -3820,16 +3798,16 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D87" s="9">
-        <v>104912</v>
+        <v>0</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -3837,13 +3815,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D88" s="9">
         <v>0</v>
@@ -3854,16 +3832,16 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D89" s="9">
-        <v>11420</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -3871,16 +3849,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C90" s="8" t="s">
         <v>171</v>
       </c>
+      <c r="C90" s="23" t="s">
+        <v>172</v>
+      </c>
       <c r="D90" s="9">
-        <v>0</v>
+        <v>45138</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -3888,16 +3866,16 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D91" s="9">
-        <v>1925</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -3905,13 +3883,13 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D92" s="9">
         <v>0</v>
@@ -3922,16 +3900,16 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C93" s="10" t="s">
         <v>177</v>
       </c>
+      <c r="C93" s="8" t="s">
+        <v>178</v>
+      </c>
       <c r="D93" s="9">
-        <v>38444</v>
+        <v>0</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -3939,16 +3917,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D94" s="9">
-        <v>0</v>
+        <v>-1423</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -3956,13 +3934,13 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D95" s="9">
         <v>0</v>
@@ -3973,16 +3951,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D96" s="9">
-        <v>0</v>
+        <v>3420</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -3990,16 +3968,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D97" s="9">
-        <v>4116</v>
+        <v>67092</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -4007,16 +3985,17 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D98" s="9">
-        <v>0</v>
+        <f>17218-8849</f>
+        <v>8369</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -4024,16 +4003,16 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D99" s="9">
-        <v>0</v>
+        <v>7830.6</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -4041,16 +4020,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D100" s="9">
-        <v>60205</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -4058,16 +4037,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D101" s="9">
-        <v>7609</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -4075,28 +4054,30 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D102" s="9"/>
+        <v>196</v>
+      </c>
+      <c r="D102" s="9">
+        <v>0</v>
+      </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="D103" s="9">
         <v>0</v>
@@ -4107,7 +4088,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>198</v>
@@ -4124,7 +4105,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>200</v>
@@ -4133,7 +4114,8 @@
         <v>201</v>
       </c>
       <c r="D105" s="9">
-        <v>14772</v>
+        <f>28560-6564-12000</f>
+        <v>9996</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -4141,16 +4123,16 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="D106" s="9">
-        <v>3640</v>
+        <v>0</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
@@ -4158,16 +4140,16 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D107" s="9">
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -4175,16 +4157,16 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D108" s="9">
-        <v>23546</v>
+        <v>0</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -4192,16 +4174,17 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D109" s="9">
-        <v>0</v>
+        <f>22754-6869-9343</f>
+        <v>6542</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -4209,16 +4192,16 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D110" s="9">
-        <v>0</v>
+        <v>24879</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -4226,16 +4209,16 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D111" s="9">
-        <v>-50</v>
+        <v>4195</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
@@ -4243,16 +4226,16 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D112" s="9">
-        <v>15390</v>
+        <v>15982</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
@@ -4260,16 +4243,16 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D113" s="9">
-        <v>21079</v>
+        <v>0</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -4277,13 +4260,13 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D114" s="9">
         <v>0</v>
@@ -4294,16 +4277,17 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C115" s="8" t="s">
         <v>220</v>
       </c>
+      <c r="C115" s="23" t="s">
+        <v>221</v>
+      </c>
       <c r="D115" s="9">
-        <v>12299</v>
+        <f>7559-10473</f>
+        <v>-2914</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -4311,16 +4295,16 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D116" s="9">
-        <v>-8</v>
+        <v>-6173</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
@@ -4328,16 +4312,16 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D117" s="9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
@@ -4345,16 +4329,16 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C118" s="10" t="s">
         <v>226</v>
       </c>
+      <c r="C118" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="D118" s="9">
-        <v>5788</v>
+        <v>0</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -4362,16 +4346,16 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D119" s="9">
-        <v>-6173</v>
+        <v>0</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
@@ -4379,16 +4363,17 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D120" s="9">
-        <v>0</v>
+        <f>30424-38255</f>
+        <v>-7831</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -4396,16 +4381,16 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D121" s="9">
-        <v>11143</v>
+        <v>4135</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
@@ -4413,16 +4398,16 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D122" s="9">
-        <v>17818</v>
+        <v>0</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
@@ -4430,16 +4415,16 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D123" s="9">
-        <v>25385</v>
+        <v>0</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -4447,13 +4432,13 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D124" s="9">
         <v>0</v>
@@ -4464,16 +4449,16 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D125" s="9">
-        <v>3788</v>
+        <v>0</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -4481,13 +4466,13 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D126" s="9">
         <v>0</v>
@@ -4498,16 +4483,16 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D127" s="9">
-        <v>0</v>
+        <v>44674</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -4515,16 +4500,16 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D128" s="9">
-        <v>19192</v>
+        <v>0</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -4532,16 +4517,16 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D129" s="9">
-        <v>0</v>
+        <v>15878</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -4549,16 +4534,16 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D130" s="9">
-        <v>38175</v>
+        <v>0</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -4566,16 +4551,16 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D131" s="9">
-        <v>0</v>
+        <v>3353</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
@@ -4583,16 +4568,16 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D132" s="9">
-        <v>13875</v>
+        <v>0</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
@@ -4600,16 +4585,17 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D133" s="9">
-        <v>0</v>
+        <f>21606-14777</f>
+        <v>6829</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
@@ -4617,16 +4603,17 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D134" s="9">
-        <v>0</v>
+        <f>11135-5000</f>
+        <v>6135</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
@@ -4634,16 +4621,17 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D135" s="9">
-        <v>0</v>
+        <f>27397-23000</f>
+        <v>4397</v>
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
@@ -4651,16 +4639,16 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" s="9">
-        <v>14777</v>
+        <v>0</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
@@ -4668,16 +4656,16 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D137" s="9">
-        <v>416</v>
+        <v>12384</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
@@ -4685,16 +4673,16 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D138" s="9">
-        <v>6364</v>
+        <v>6696</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
@@ -4702,16 +4690,17 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D139" s="9">
-        <v>22340</v>
+        <f>4296-4300</f>
+        <v>-4</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
@@ -4719,13 +4708,13 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D140" s="9">
         <v>0</v>
@@ -4736,16 +4725,16 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D141" s="9">
-        <v>10038</v>
+        <v>15646</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
@@ -4753,13 +4742,13 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D142" s="9">
         <v>0</v>
@@ -4770,16 +4759,16 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D143" s="9">
-        <v>0</v>
+        <v>46889</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
@@ -4787,13 +4776,13 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D144" s="9">
         <v>0</v>
@@ -4804,13 +4793,13 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D145" s="9">
         <v>0</v>
@@ -4821,16 +4810,16 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>280</v>
+        <v>74</v>
       </c>
       <c r="D146" s="9">
-        <v>11906</v>
+        <v>33970</v>
       </c>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
@@ -4838,16 +4827,16 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D147" s="9">
-        <v>4454</v>
+        <v>4615</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
@@ -4855,16 +4844,16 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D148" s="9">
-        <v>40876</v>
+        <v>5119</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
@@ -4872,16 +4861,16 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D149" s="9">
-        <v>0</v>
+        <v>11932</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
@@ -4889,13 +4878,13 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D150" s="9">
         <v>0</v>
@@ -4906,16 +4895,16 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>75</v>
+        <v>292</v>
       </c>
       <c r="D151" s="9">
-        <v>28972</v>
+        <v>0</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
@@ -4923,16 +4912,17 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D152" s="9">
-        <v>0</v>
+        <f>14904-6984-5000</f>
+        <v>2920</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
@@ -4940,13 +4930,13 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D153" s="9">
         <v>0</v>
@@ -4957,16 +4947,16 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D154" s="9">
-        <v>5333</v>
+        <v>0</v>
       </c>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
@@ -4974,13 +4964,13 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D155" s="9">
         <v>0</v>
@@ -4991,16 +4981,16 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D156" s="9">
-        <v>6573</v>
+        <v>0</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
@@ -5008,16 +4998,16 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D157" s="9">
-        <v>1673</v>
+        <v>12083</v>
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
@@ -5025,16 +5015,16 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D158" s="9">
-        <v>10717</v>
+        <v>0</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
@@ -5042,16 +5032,16 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D159" s="9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
@@ -5059,16 +5049,17 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D160" s="9">
-        <v>10816</v>
+        <f>6324-1660</f>
+        <v>4664</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
@@ -5076,16 +5067,17 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D161" s="9">
-        <v>0</v>
+        <f>39472-4352-43428</f>
+        <v>-8308</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
@@ -5093,16 +5085,16 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D162" s="9">
-        <v>0</v>
+        <v>10574</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
@@ -5110,16 +5102,16 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D163" s="9">
-        <v>9480</v>
+        <v>0</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
@@ -5127,16 +5119,16 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D164" s="9">
-        <v>9555</v>
+        <v>0</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
@@ -5144,13 +5136,13 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D165" s="9">
         <v>0</v>
@@ -5161,16 +5153,16 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="D166" s="9">
-        <v>4573</v>
+        <v>0</v>
       </c>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
@@ -5178,16 +5170,16 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D167" s="9">
-        <v>36705</v>
+        <v>0</v>
       </c>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
@@ -5195,16 +5187,16 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D168" s="9">
-        <v>6119</v>
+        <v>0</v>
       </c>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
@@ -5212,16 +5204,16 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D169" s="9">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
@@ -5229,16 +5221,17 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D170" s="9">
-        <v>0</v>
+        <f>12980-15000</f>
+        <v>-2020</v>
       </c>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
@@ -5246,16 +5239,16 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D171" s="9">
-        <v>0</v>
+        <v>53998</v>
       </c>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
@@ -5263,16 +5256,16 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D172" s="9">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
@@ -5280,16 +5273,16 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="D173" s="9">
-        <v>0</v>
+        <v>8503</v>
       </c>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
@@ -5297,13 +5290,13 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D174" s="9">
         <v>0</v>
@@ -5314,16 +5307,16 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D175" s="9">
-        <v>22796</v>
+        <v>0</v>
       </c>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
@@ -5331,16 +5324,16 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D176" s="9">
-        <v>3138</v>
+        <v>0</v>
       </c>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
@@ -5348,16 +5341,16 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D177" s="9">
-        <v>2571</v>
+        <v>0</v>
       </c>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
@@ -5365,16 +5358,16 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D178" s="9">
-        <v>51096</v>
+        <v>0</v>
       </c>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
@@ -5382,13 +5375,13 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D179" s="9">
         <v>0</v>
@@ -5399,16 +5392,16 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D180" s="9">
-        <v>6028</v>
+        <v>0</v>
       </c>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
@@ -5416,16 +5409,16 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D181" s="9">
-        <v>0</v>
+        <v>3718</v>
       </c>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
@@ -5433,16 +5426,16 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D182" s="9">
-        <v>14139</v>
+        <v>4684</v>
       </c>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
@@ -5450,13 +5443,13 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D183" s="9">
         <v>0</v>
@@ -5467,13 +5460,13 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D184" s="9">
         <v>0</v>
@@ -5484,13 +5477,13 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D185" s="9">
         <v>0</v>
@@ -5501,16 +5494,16 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D186" s="9">
-        <v>2499</v>
+        <v>0</v>
       </c>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
@@ -5518,16 +5511,17 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>357</v>
+        <v>361</v>
+      </c>
+      <c r="C187" s="23" t="s">
+        <v>362</v>
       </c>
       <c r="D187" s="9">
-        <v>0</v>
+        <f>54491-4910</f>
+        <v>49581</v>
       </c>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
@@ -5535,13 +5529,13 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D188" s="9">
         <v>0</v>
@@ -5552,16 +5546,16 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D189" s="9">
-        <v>0</v>
+        <v>55873</v>
       </c>
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
@@ -5569,13 +5563,13 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D190" s="9">
         <v>0</v>
@@ -5586,16 +5580,16 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D191" s="9">
-        <v>0</v>
+        <v>98828</v>
       </c>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
@@ -5603,16 +5597,16 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="D192" s="9">
-        <v>6203</v>
+        <v>0</v>
       </c>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
@@ -5620,16 +5614,16 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D193" s="9">
-        <v>20</v>
+        <v>6262</v>
       </c>
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
@@ -5637,16 +5631,16 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D194" s="9">
-        <v>2079</v>
+        <v>0</v>
       </c>
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
@@ -5654,13 +5648,13 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D195" s="9">
         <v>0</v>
@@ -5671,16 +5665,16 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="C196" s="10" t="s">
-        <v>373</v>
+        <v>378</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="D196" s="9">
-        <v>46947</v>
+        <v>0</v>
       </c>
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
@@ -5688,16 +5682,16 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D197" s="9">
-        <v>0</v>
+        <v>-28619</v>
       </c>
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
@@ -5705,16 +5699,16 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D198" s="9">
-        <v>50405</v>
+        <v>15869</v>
       </c>
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
@@ -5722,16 +5716,16 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D199" s="9">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
@@ -5739,16 +5733,16 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D200" s="9">
-        <v>93773</v>
+        <v>0</v>
       </c>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
@@ -5756,13 +5750,13 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>24</v>
+        <v>389</v>
       </c>
       <c r="D201" s="9">
         <v>0</v>
@@ -5773,16 +5767,16 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D202" s="9">
-        <v>3329</v>
+        <v>2466</v>
       </c>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
@@ -5790,16 +5784,16 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D203" s="9">
-        <v>15281</v>
+        <v>0</v>
       </c>
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
@@ -5807,16 +5801,17 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="D204" s="9">
-        <v>0</v>
+        <f>13970-17504</f>
+        <v>-3534</v>
       </c>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
@@ -5824,13 +5819,13 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D205" s="9">
         <v>0</v>
@@ -5841,16 +5836,17 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D206" s="9">
-        <v>-30216.316666666666</v>
+        <f>10110-2500-5000</f>
+        <v>2610</v>
       </c>
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
@@ -5858,16 +5854,16 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>394</v>
+        <v>149</v>
       </c>
       <c r="D207" s="9">
-        <v>13231</v>
+        <v>2701</v>
       </c>
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
@@ -5875,13 +5871,13 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D208" s="9">
         <v>0</v>
@@ -5892,16 +5888,16 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D209" s="9">
-        <v>0</v>
+        <v>6693</v>
       </c>
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
@@ -5909,13 +5905,13 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D210" s="9">
         <v>0</v>
@@ -5926,13 +5922,13 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D211" s="9">
         <v>0</v>
@@ -5943,16 +5939,16 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D212" s="9">
-        <v>-83</v>
+        <v>0</v>
       </c>
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
@@ -5960,16 +5956,16 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D213" s="9">
-        <v>11504</v>
+        <v>0</v>
       </c>
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
@@ -5977,13 +5973,13 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D214" s="9">
         <v>0</v>
@@ -5994,16 +5990,16 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D215" s="9">
-        <v>7919</v>
+        <v>0</v>
       </c>
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
@@ -6011,16 +6007,16 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>153</v>
+        <v>418</v>
       </c>
       <c r="D216" s="9">
-        <v>3357</v>
+        <v>10721</v>
       </c>
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
@@ -6028,16 +6024,16 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D217" s="9">
-        <v>10235</v>
+        <v>12876</v>
       </c>
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
@@ -6045,16 +6041,16 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D218" s="9">
-        <v>3222</v>
+        <v>3227</v>
       </c>
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
@@ -6062,16 +6058,16 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="D219" s="9">
-        <v>3313</v>
+        <v>10999</v>
       </c>
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
@@ -6079,16 +6075,16 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D220" s="9">
-        <v>0</v>
+        <v>20242</v>
       </c>
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
@@ -6096,16 +6092,16 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="D221" s="9">
-        <v>14008</v>
+        <v>0</v>
       </c>
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
@@ -6113,16 +6109,16 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D222" s="9">
-        <v>0</v>
+        <v>2310</v>
       </c>
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
@@ -6130,16 +6126,16 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="D223" s="9">
-        <v>0</v>
+        <v>23461</v>
       </c>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
@@ -6147,16 +6143,16 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D224" s="9">
-        <v>0</v>
+        <v>8261</v>
       </c>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
@@ -6164,16 +6160,16 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D225" s="9">
-        <v>5507</v>
+        <v>0</v>
       </c>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
@@ -6181,16 +6177,16 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D226" s="9">
-        <v>9555</v>
+        <v>0</v>
       </c>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
@@ -6198,16 +6194,16 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="D227" s="9">
-        <v>1598</v>
+        <v>431618</v>
       </c>
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
@@ -6215,16 +6211,16 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D228" s="9">
-        <v>7872</v>
+        <v>4163</v>
       </c>
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
@@ -6232,16 +6228,16 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D229" s="9">
-        <v>12648</v>
+        <v>0</v>
       </c>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
@@ -6249,16 +6245,17 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D230" s="9">
-        <v>0</v>
+        <f>10754-8000</f>
+        <v>2754</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
@@ -6266,16 +6263,17 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D231" s="9">
-        <v>-102.76466666667056</v>
+        <f>5914-2449</f>
+        <v>3465</v>
       </c>
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
@@ -6283,16 +6281,16 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D232" s="9">
-        <v>18122</v>
+        <v>0</v>
       </c>
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
@@ -6300,16 +6298,17 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D233" s="9">
-        <v>6234</v>
+        <f>11298-6774</f>
+        <v>4524</v>
       </c>
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
@@ -6317,16 +6316,16 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B234" s="8" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D234" s="9">
-        <v>0</v>
+        <v>62133</v>
       </c>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
@@ -6334,16 +6333,16 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D235" s="9">
-        <v>12999</v>
+        <v>13195</v>
       </c>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
@@ -6351,16 +6350,16 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="D236" s="9">
-        <v>418115</v>
+        <v>0</v>
       </c>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
@@ -6368,16 +6367,16 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C237" s="8" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="D237" s="9">
-        <v>0</v>
+        <v>1727</v>
       </c>
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
@@ -6385,16 +6384,16 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C238" s="8" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="D238" s="9">
-        <v>2571</v>
+        <v>1717</v>
       </c>
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
@@ -6402,284 +6401,129 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C239" s="8" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D239" s="9">
-        <v>8302</v>
+        <v>0</v>
       </c>
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
       <c r="G239" s="3"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A240" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B240" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="C240" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D240" s="9">
-        <v>3150</v>
-      </c>
-      <c r="E240" s="3"/>
-      <c r="F240" s="3"/>
-      <c r="G240" s="3"/>
+      <c r="A240" s="10"/>
+      <c r="B240" s="10"/>
+      <c r="C240" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="D240" s="12"/>
+      <c r="E240" s="13"/>
+      <c r="F240" s="13"/>
+      <c r="G240" s="13"/>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A241" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B241" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="C241" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="D241" s="9">
-        <v>0</v>
-      </c>
+      <c r="A241" s="14"/>
+      <c r="B241" s="14"/>
+      <c r="C241" s="14"/>
+      <c r="D241" s="15"/>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A242" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B242" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="C242" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="D242" s="9">
-        <v>6641</v>
-      </c>
+      <c r="A242" s="14"/>
+      <c r="B242" s="14"/>
+      <c r="C242" s="14"/>
+      <c r="D242" s="15"/>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A243" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B243" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="C243" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="D243" s="9">
-        <v>56890</v>
-      </c>
+      <c r="A243" s="14"/>
+      <c r="B243" s="14"/>
+      <c r="C243" s="14"/>
+      <c r="D243" s="15"/>
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
       <c r="G243" s="3"/>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A244" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B244" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="C244" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="D244" s="9">
-        <v>9868</v>
-      </c>
+      <c r="A244" s="14"/>
+      <c r="B244" s="14"/>
+      <c r="C244" s="14"/>
+      <c r="D244" s="15"/>
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
       <c r="G244" s="3"/>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A245" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B245" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="C245" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="D245" s="9">
-        <v>0</v>
-      </c>
+      <c r="A245" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="B245" s="14"/>
+      <c r="C245" s="14"/>
+      <c r="D245" s="15"/>
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3"/>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A246" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B246" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="C246" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="D246" s="9">
-        <v>0</v>
-      </c>
+      <c r="A246" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="B246" s="14"/>
+      <c r="C246" s="14"/>
+      <c r="D246" s="15"/>
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="G246" s="3"/>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A247" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B247" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="C247" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="D247" s="9">
-        <v>0</v>
-      </c>
+      <c r="A247" s="14"/>
+      <c r="B247" s="14"/>
+      <c r="C247" s="14"/>
+      <c r="D247" s="15"/>
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
       <c r="G247" s="3"/>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A248" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B248" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="C248" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="D248" s="9">
-        <v>184</v>
-      </c>
-      <c r="E248" s="3"/>
-      <c r="F248" s="3"/>
-      <c r="G248" s="3"/>
+      <c r="A248" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="B248" s="16"/>
+      <c r="C248" s="16"/>
+      <c r="D248" s="15"/>
+      <c r="E248" s="17"/>
+      <c r="F248" s="17"/>
+      <c r="G248" s="17"/>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A249" s="11"/>
-      <c r="B249" s="11"/>
-      <c r="C249" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="D249" s="13">
-        <v>2119000.9186666664</v>
-      </c>
-      <c r="E249" s="14"/>
-      <c r="F249" s="14"/>
-      <c r="G249" s="14"/>
+      <c r="A249" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="B249" s="16"/>
+      <c r="C249" s="16"/>
+      <c r="D249" s="15"/>
+      <c r="E249" s="17"/>
+      <c r="F249" s="17"/>
+      <c r="G249" s="17"/>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A250" s="15"/>
-      <c r="B250" s="15"/>
-      <c r="C250" s="15"/>
-      <c r="D250" s="16"/>
+      <c r="A250" s="14"/>
+      <c r="B250" s="14"/>
+      <c r="C250" s="14"/>
+      <c r="D250" s="15"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="G250" s="3"/>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A251" s="15"/>
-      <c r="B251" s="15"/>
-      <c r="C251" s="15"/>
-      <c r="D251" s="16"/>
-      <c r="E251" s="3"/>
-      <c r="F251" s="3"/>
-      <c r="G251" s="3"/>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A252" s="15"/>
-      <c r="B252" s="15"/>
-      <c r="C252" s="15"/>
-      <c r="D252" s="16"/>
-      <c r="E252" s="3"/>
-      <c r="F252" s="3"/>
-      <c r="G252" s="3"/>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A253" s="15"/>
-      <c r="B253" s="15"/>
-      <c r="C253" s="15"/>
-      <c r="D253" s="16"/>
-      <c r="E253" s="3"/>
-      <c r="F253" s="3"/>
-      <c r="G253" s="3"/>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A254" s="17" t="s">
-        <v>477</v>
-      </c>
-      <c r="B254" s="15"/>
-      <c r="C254" s="15"/>
-      <c r="D254" s="16"/>
-      <c r="E254" s="3"/>
-      <c r="F254" s="3"/>
-      <c r="G254" s="3"/>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A255" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="B255" s="15"/>
-      <c r="C255" s="15"/>
-      <c r="D255" s="16"/>
-      <c r="E255" s="3"/>
-      <c r="F255" s="3"/>
-      <c r="G255" s="3"/>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A256" s="15"/>
-      <c r="B256" s="15"/>
-      <c r="C256" s="15"/>
-      <c r="D256" s="16"/>
-      <c r="E256" s="3"/>
-      <c r="F256" s="3"/>
-      <c r="G256" s="3"/>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A257" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="B257" s="17"/>
-      <c r="C257" s="17"/>
-      <c r="D257" s="16"/>
-      <c r="E257" s="18"/>
-      <c r="F257" s="18"/>
-      <c r="G257" s="18"/>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A258" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="B258" s="17"/>
-      <c r="C258" s="17"/>
-      <c r="D258" s="16"/>
-      <c r="E258" s="18"/>
-      <c r="F258" s="18"/>
-      <c r="G258" s="18"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A259" s="15"/>
-      <c r="B259" s="15"/>
-      <c r="C259" s="15"/>
-      <c r="D259" s="16"/>
-      <c r="E259" s="3"/>
-      <c r="F259" s="3"/>
-      <c r="G259" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
